--- a/utils/data-room-simulator/output/cash_flow.xlsx
+++ b/utils/data-room-simulator/output/cash_flow.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Cash Flow" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,77 +417,77 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>net_income</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>depreciation</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>ar_change</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>inventory_change</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>prepaid_change</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ap_change</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>accrued_change</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>deferred_change</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>cash_from_operations</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>capex</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>cash_from_investing</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>cash_from_financing</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>net_change_in_cash</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>ending_cash</t>
         </is>
@@ -510,46 +498,46 @@
         <v>2021</v>
       </c>
       <c r="B2" t="n">
-        <v>8380075.79</v>
+        <v>3447875.81</v>
       </c>
       <c r="C2" t="n">
-        <v>372020.04</v>
+        <v>201343.13</v>
       </c>
       <c r="D2" t="n">
-        <v>-6102853.62</v>
+        <v>-3944970.63</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-83915.96000000001</v>
+        <v>-53447.76</v>
       </c>
       <c r="G2" t="n">
-        <v>1760429.06</v>
+        <v>991313.83</v>
       </c>
       <c r="H2" t="n">
-        <v>125873.95</v>
+        <v>80171.64</v>
       </c>
       <c r="I2" t="n">
-        <v>5832440.58</v>
+        <v>3893107.89</v>
       </c>
       <c r="J2" t="n">
-        <v>10284069.84</v>
+        <v>4615393.91</v>
       </c>
       <c r="K2" t="n">
-        <v>-965185.3199999999</v>
+        <v>-527966.4399999999</v>
       </c>
       <c r="L2" t="n">
-        <v>-965185.3199999999</v>
+        <v>-527966.4399999999</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>9318884.52</v>
+        <v>4087427.47</v>
       </c>
       <c r="O2" t="n">
-        <v>6036389.43</v>
+        <v>2278794.93</v>
       </c>
     </row>
     <row r="3">
@@ -557,46 +545,46 @@
         <v>2022</v>
       </c>
       <c r="B3" t="n">
-        <v>8775501.869999999</v>
+        <v>4462964.54</v>
       </c>
       <c r="C3" t="n">
-        <v>389492.6</v>
+        <v>210799.57</v>
       </c>
       <c r="D3" t="n">
-        <v>-380819.83</v>
+        <v>-1384773.74</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-3050.86</v>
+        <v>-16614.28</v>
       </c>
       <c r="G3" t="n">
-        <v>159045.14</v>
+        <v>470972.25</v>
       </c>
       <c r="H3" t="n">
-        <v>4576.28</v>
+        <v>24921.42</v>
       </c>
       <c r="I3" t="n">
-        <v>-374917.18</v>
+        <v>387543.67</v>
       </c>
       <c r="J3" t="n">
-        <v>8569828.02</v>
+        <v>4155813.43</v>
       </c>
       <c r="K3" t="n">
-        <v>-148031.45</v>
+        <v>-81430.36</v>
       </c>
       <c r="L3" t="n">
-        <v>-148031.45</v>
+        <v>-81430.36</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>8421796.57</v>
+        <v>4074383.07</v>
       </c>
       <c r="O3" t="n">
-        <v>14458186.02</v>
+        <v>6353177.99</v>
       </c>
     </row>
     <row r="4">
@@ -604,46 +592,46 @@
         <v>2023</v>
       </c>
       <c r="B4" t="n">
-        <v>9250546.75</v>
+        <v>5345324.69</v>
       </c>
       <c r="C4" t="n">
-        <v>406965.16</v>
+        <v>220255.99</v>
       </c>
       <c r="D4" t="n">
-        <v>-427758.23</v>
+        <v>-998546.6</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-7554.92</v>
+        <v>-10774.28</v>
       </c>
       <c r="G4" t="n">
-        <v>-74321.77</v>
+        <v>224508.32</v>
       </c>
       <c r="H4" t="n">
-        <v>11332.38</v>
+        <v>16161.41</v>
       </c>
       <c r="I4" t="n">
-        <v>77668.55</v>
+        <v>1072117.05</v>
       </c>
       <c r="J4" t="n">
-        <v>9236877.92</v>
+        <v>5869046.58</v>
       </c>
       <c r="K4" t="n">
-        <v>-148031.46</v>
+        <v>-81430.36</v>
       </c>
       <c r="L4" t="n">
-        <v>-148031.46</v>
+        <v>-81430.36</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>9088846.460000001</v>
+        <v>5787616.22</v>
       </c>
       <c r="O4" t="n">
-        <v>23547032.47</v>
+        <v>12140794.24</v>
       </c>
     </row>
     <row r="5">
@@ -651,46 +639,46 @@
         <v>2024</v>
       </c>
       <c r="B5" t="n">
-        <v>9583498.67</v>
+        <v>6126650.31</v>
       </c>
       <c r="C5" t="n">
-        <v>424437.74</v>
+        <v>229712.42</v>
       </c>
       <c r="D5" t="n">
-        <v>-2224840.9</v>
+        <v>-671892.36</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-16104.29</v>
+        <v>-14133.96</v>
       </c>
       <c r="G5" t="n">
-        <v>-53043.98</v>
+        <v>740550.62</v>
       </c>
       <c r="H5" t="n">
-        <v>24156.44</v>
+        <v>21200.95</v>
       </c>
       <c r="I5" t="n">
-        <v>-102394.99</v>
+        <v>476662.32</v>
       </c>
       <c r="J5" t="n">
-        <v>7635708.69</v>
+        <v>6908750.3</v>
       </c>
       <c r="K5" t="n">
-        <v>-148031.45</v>
+        <v>-81430.36</v>
       </c>
       <c r="L5" t="n">
-        <v>-148031.45</v>
+        <v>-81430.36</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>7487677.24</v>
+        <v>6827319.94</v>
       </c>
       <c r="O5" t="n">
-        <v>31034709.67</v>
+        <v>18968114.18</v>
       </c>
     </row>
     <row r="6">
@@ -698,46 +686,46 @@
         <v>2025</v>
       </c>
       <c r="B6" t="n">
-        <v>11638456.64</v>
+        <v>7456175.01</v>
       </c>
       <c r="C6" t="n">
-        <v>441910.29</v>
+        <v>239168.85</v>
       </c>
       <c r="D6" t="n">
-        <v>-621383.9</v>
+        <v>-1829040.61</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>-15409.31</v>
+        <v>-17210.43</v>
       </c>
       <c r="G6" t="n">
-        <v>942102.61</v>
+        <v>-203680.61</v>
       </c>
       <c r="H6" t="n">
-        <v>23113.97</v>
+        <v>25815.64</v>
       </c>
       <c r="I6" t="n">
-        <v>1505753.16</v>
+        <v>430504.51</v>
       </c>
       <c r="J6" t="n">
-        <v>13914543.46</v>
+        <v>6101732.36</v>
       </c>
       <c r="K6" t="n">
-        <v>-148031.46</v>
+        <v>-81430.37</v>
       </c>
       <c r="L6" t="n">
-        <v>-148031.46</v>
+        <v>-81430.37</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>13766512</v>
+        <v>6020301.99</v>
       </c>
       <c r="O6" t="n">
-        <v>44801221.68</v>
+        <v>24988416.19</v>
       </c>
     </row>
     <row r="7">
@@ -745,46 +733,46 @@
         <v>2026</v>
       </c>
       <c r="B7" t="n">
-        <v>901119.76</v>
+        <v>1176546.48</v>
       </c>
       <c r="C7" t="n">
-        <v>37614.55</v>
+        <v>40780.85</v>
       </c>
       <c r="D7" t="n">
-        <v>2437729.2</v>
+        <v>3135579.43</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>32168.7</v>
+        <v>26889</v>
       </c>
       <c r="G7" t="n">
-        <v>-689957.13</v>
+        <v>-236685.47</v>
       </c>
       <c r="H7" t="n">
-        <v>-48253.06</v>
+        <v>-40333.5</v>
       </c>
       <c r="I7" t="n">
-        <v>-1497077.05</v>
+        <v>-1501483.95</v>
       </c>
       <c r="J7" t="n">
-        <v>1173344.97</v>
+        <v>2601292.84</v>
       </c>
       <c r="K7" t="n">
-        <v>-12335.95</v>
+        <v>-13571.72</v>
       </c>
       <c r="L7" t="n">
-        <v>-12335.95</v>
+        <v>-13571.72</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1161009.02</v>
+        <v>2587721.12</v>
       </c>
       <c r="O7" t="n">
-        <v>45962230.7</v>
+        <v>27576137.3</v>
       </c>
     </row>
   </sheetData>
